--- a/projects/promo-value-creation/deliverables/WS1_Campaign_Discovery_and_Gap_Analysis.xlsx
+++ b/projects/promo-value-creation/deliverables/WS1_Campaign_Discovery_and_Gap_Analysis.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rbdd2685cbac14b1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campaign Inventory" sheetId="2" r:id="Re4a0bec14fc14982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Summary" sheetId="3" r:id="R0e1ba2f795de4257"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segment Map" sheetId="4" r:id="Rd8ccc4b5f0f84438"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Source Map" sheetId="5" r:id="Rd1c9dbb6165943e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Tracker" sheetId="6" r:id="Reecd4e408b294cf7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="R75ef1200068a4ba5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R001f02982c224556"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campaign Inventory" sheetId="2" r:id="R501d1fd82ea1498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Summary" sheetId="3" r:id="R9def61b7b9084dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segment Map" sheetId="4" r:id="Ref2c341745e349fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Source Map" sheetId="5" r:id="R1cb78d0ff57642b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action Tracker" sheetId="6" r:id="R56edab119b424644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" r:id="Rf931bd4d7ca54131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AM Code Register" sheetId="8" r:id="R2cc0ef4578f94c4a"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Brands">'Lists'!$A$2:$A$2</x:definedName>
@@ -104,11 +105,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="165" formatCode="0&quot;%&quot;"/>
+    <x:numFmt numFmtId="200" formatCode="#,##0"/>
+    <x:numFmt numFmtId="201" formatCode="0%"/>
+    <x:numFmt numFmtId="202" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -177,8 +181,30 @@
       <x:color rgb="FF172033"/>
       <x:name val="Aptos Display"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF17324D"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF35576D"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17324D"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="18">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -240,8 +266,33 @@
         <x:fgColor rgb="FFECEEF2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EDED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F6F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="13">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
@@ -253,11 +304,115 @@
         <x:color rgb="FFBF9440"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C7D1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C7D1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C7D1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C7D1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6EDF1"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2E8"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="85">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -329,11 +484,137 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="16" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="6">
+  <x:dxfs count="8">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -385,6 +666,28 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="00DFF0E5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFA61B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE2E1"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF2F641C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -925,7 +1228,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1de7cf6c42dd475e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R95f22db5dcb949b9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -950,7 +1253,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbbc33bbe5a314e0a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R27ce3171af5c4ac8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -975,7 +1278,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R445c5e51a4c44278"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdf2be01b6dd34256"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1000,7 +1303,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R83fb9f9dfdfc4083"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re5db53e410024e7d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1213,6 +1516,38 @@
     <x:tableColumn id="16" name="Follow-up required"/>
     <x:tableColumn id="17" name="Last updated"/>
     <x:tableColumn id="18" name="Notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="AMCodeRegisterTable" displayName="AMCodeRegisterTable" ref="A6:W79" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:W79"/>
+  <x:tableColumns count="23">
+    <x:tableColumn id="1" name="Register ID"/>
+    <x:tableColumn id="2" name="Source row"/>
+    <x:tableColumn id="3" name="Campaign source"/>
+    <x:tableColumn id="4" name="Source owner"/>
+    <x:tableColumn id="5" name="Bonus mechanic (source)"/>
+    <x:tableColumn id="6" name="Raw code cell"/>
+    <x:tableColumn id="7" name="Promo code"/>
+    <x:tableColumn id="8" name="Site / brand evidence"/>
+    <x:tableColumn id="9" name="Campaign type"/>
+    <x:tableColumn id="10" name="Bonus type"/>
+    <x:tableColumn id="11" name="Bonus %"/>
+    <x:tableColumn id="12" name="Fixed reward value"/>
+    <x:tableColumn id="13" name="Minimum deposit"/>
+    <x:tableColumn id="14" name="Maximum bonus cap"/>
+    <x:tableColumn id="15" name="TO requirement"/>
+    <x:tableColumn id="16" name="Validity days"/>
+    <x:tableColumn id="17" name="Game / product"/>
+    <x:tableColumn id="18" name="Code status"/>
+    <x:tableColumn id="19" name="Confirmation needed"/>
+    <x:tableColumn id="20" name="Source URL"/>
+    <x:tableColumn id="21" name="Received date"/>
+    <x:tableColumn id="22" name="Exact WS1 inventory match"/>
+    <x:tableColumn id="23" name="Matching campaign ID"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1453,7 +1788,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
-        <x:v>Working workbook updated with real WS1 evidence observed from 2026-01-01 to 2026-07-23. Jan–Mar records are assignment-based; Apr–Jul records are approved bonus executions.</x:v>
+        <x:v>Real WS1 evidence is loaded through 2026-07-23. Kevin's AM Team code workbook is compiled in a separate register; site, monthly/ad hoc classification, active period, objective and segment still require confirmation.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2005,7 +2340,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
-        <x:v>Real WS1 promo-code evidence loaded. Yellow cells need business confirmation; blue cells calculate readiness. Apr–Jul executions do not provide an assignment denominator.</x:v>
+        <x:v>Real WS1 promo-code evidence loaded. Kevin's AM code list is held in a separate register and is not included in the WS1 campaign count until site, calendar and campaign context are confirmed.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -31103,9 +31438,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00639e8239b34d1b"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d1bdcc2a82b4256"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6b8dd81aad04555"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R098e583916eb4f31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31175,7 +31510,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2" t="str">
-        <x:v>Management view based on 26 observed WS1 promo codes. Campaign objectives, segment rules, owners and planned success targets still require source-team confirmation.</x:v>
+        <x:v>Management view based on 26 observed WS1 promo codes. The separate AM register is excluded from these counts until its site and campaign context are confirmed.</x:v>
       </x:c>
       <x:c r="AA2" t="inlineStr">
         <x:is>
@@ -34056,10 +34391,10 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d38d9deaa4b436d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dc882bde97541b0"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc111ff59f254237"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc11982329e8451a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf328c883f54401f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R291c77d5c3d74ed4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37008,7 +37343,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd77b31801fb848a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92dedc3f7e504b57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40023,7 +40358,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fc5c314c9614dc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53e54c93cba14d29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40360,12 +40695,14 @@
         <x:v>46231</x:v>
       </x:c>
       <x:c r="M10" s="17" t="str">
-        <x:v>Waiting for Response</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="N10" s="18" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="O10" s="17"/>
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="O10" s="17" t="str">
+        <x:v>Kevin workbook received and compiled: 64 source rows, 72 individual code entries and 68 unique codes.</x:v>
+      </x:c>
       <x:c r="P10" s="17" t="str">
         <x:v>Yes</x:v>
       </x:c>
@@ -40373,7 +40710,7 @@
         <x:v>46226</x:v>
       </x:c>
       <x:c r="R10" s="17" t="str">
-        <x:v>Specific contact: Kevin, AM TL.</x:v>
+        <x:v>Code list received. Site/brand, monthly vs ad hoc, active period, objective and segment are not supplied. 1 source row has no promo code; combined-code cells were split for review.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -42562,7 +42899,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2685ea66dba40b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra834fd3dcc574f37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44002,4 +44339,4912 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="46" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="13" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="34" t="str">
+        <x:v>AM Team Promo Code Register</x:v>
+      </x:c>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="34"/>
+      <x:c r="D1" s="34"/>
+      <x:c r="E1" s="34"/>
+      <x:c r="F1" s="34"/>
+      <x:c r="G1" s="34"/>
+      <x:c r="H1" s="34"/>
+      <x:c r="I1" s="34"/>
+      <x:c r="J1" s="34"/>
+      <x:c r="K1" s="34"/>
+      <x:c r="L1" s="34"/>
+      <x:c r="M1" s="34"/>
+      <x:c r="N1" s="34"/>
+      <x:c r="O1" s="34"/>
+      <x:c r="P1" s="34"/>
+      <x:c r="Q1" s="34"/>
+      <x:c r="R1" s="34"/>
+      <x:c r="S1" s="34"/>
+      <x:c r="T1" s="34"/>
+      <x:c r="U1" s="34"/>
+      <x:c r="V1" s="34"/>
+      <x:c r="W1" s="34"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="38" t="str">
+        <x:v>Source owner: Kevin | Source team: AM | Received 2026-07-23 | Source contains promo mechanics and codes only; campaign timing and site context remain incomplete.</x:v>
+      </x:c>
+      <x:c r="B2" s="38"/>
+      <x:c r="C2" s="38"/>
+      <x:c r="D2" s="38"/>
+      <x:c r="E2" s="38"/>
+      <x:c r="F2" s="38"/>
+      <x:c r="G2" s="38"/>
+      <x:c r="H2" s="38"/>
+      <x:c r="I2" s="38"/>
+      <x:c r="J2" s="38"/>
+      <x:c r="K2" s="38"/>
+      <x:c r="L2" s="38"/>
+      <x:c r="M2" s="38"/>
+      <x:c r="N2" s="38"/>
+      <x:c r="O2" s="38"/>
+      <x:c r="P2" s="38"/>
+      <x:c r="Q2" s="38"/>
+      <x:c r="R2" s="38"/>
+      <x:c r="S2" s="38"/>
+      <x:c r="T2" s="38"/>
+      <x:c r="U2" s="38"/>
+      <x:c r="V2" s="38"/>
+      <x:c r="W2" s="38"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="41" t="str">
+        <x:v>Source: https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="B3" s="41"/>
+      <x:c r="C3" s="41"/>
+      <x:c r="D3" s="41"/>
+      <x:c r="E3" s="41"/>
+      <x:c r="F3" s="41"/>
+      <x:c r="G3" s="41"/>
+      <x:c r="H3" s="41"/>
+      <x:c r="I3" s="41"/>
+      <x:c r="J3" s="41"/>
+      <x:c r="K3" s="41"/>
+      <x:c r="L3" s="41"/>
+      <x:c r="M3" s="41"/>
+      <x:c r="N3" s="41"/>
+      <x:c r="O3" s="41"/>
+      <x:c r="P3" s="41"/>
+      <x:c r="Q3" s="41"/>
+      <x:c r="R3" s="41"/>
+      <x:c r="S3" s="41"/>
+      <x:c r="T3" s="41"/>
+      <x:c r="U3" s="41"/>
+      <x:c r="V3" s="41"/>
+      <x:c r="W3" s="41"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="45" t="str">
+        <x:v>Register entries</x:v>
+      </x:c>
+      <x:c r="B4" s="47" t="n">
+        <x:f>COUNTA(A7:A79)</x:f>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C4" s="45"/>
+      <x:c r="D4" s="45" t="str">
+        <x:v>Individual codes</x:v>
+      </x:c>
+      <x:c r="E4" s="47" t="n">
+        <x:f>COUNTA(G7:G79)</x:f>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F4" s="45"/>
+      <x:c r="G4" s="45" t="str">
+        <x:v>Missing code</x:v>
+      </x:c>
+      <x:c r="H4" s="47" t="n">
+        <x:f>COUNTIF(R7:R79,"Missing")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I4" s="45"/>
+      <x:c r="J4" s="45" t="str">
+        <x:v>Exact WS1 matches</x:v>
+      </x:c>
+      <x:c r="K4" s="47" t="n">
+        <x:f>COUNTIF(V7:V79,"Yes")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L4" s="45"/>
+      <x:c r="M4" s="45" t="str">
+        <x:v>Needs confirmation</x:v>
+      </x:c>
+      <x:c r="N4" s="47" t="n">
+        <x:f>COUNTIF(S7:S79,"&lt;&gt;")</x:f>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="O4" s="45"/>
+      <x:c r="P4" s="45" t="str">
+        <x:v>Sensitive member fields</x:v>
+      </x:c>
+      <x:c r="Q4" s="47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="51" t="str">
+        <x:v>Register ID</x:v>
+      </x:c>
+      <x:c r="B6" s="51" t="str">
+        <x:v>Source row</x:v>
+      </x:c>
+      <x:c r="C6" s="51" t="str">
+        <x:v>Campaign source</x:v>
+      </x:c>
+      <x:c r="D6" s="51" t="str">
+        <x:v>Source owner</x:v>
+      </x:c>
+      <x:c r="E6" s="51" t="str">
+        <x:v>Bonus mechanic (source)</x:v>
+      </x:c>
+      <x:c r="F6" s="51" t="str">
+        <x:v>Raw code cell</x:v>
+      </x:c>
+      <x:c r="G6" s="51" t="str">
+        <x:v>Promo code</x:v>
+      </x:c>
+      <x:c r="H6" s="51" t="str">
+        <x:v>Site / brand evidence</x:v>
+      </x:c>
+      <x:c r="I6" s="51" t="str">
+        <x:v>Campaign type</x:v>
+      </x:c>
+      <x:c r="J6" s="51" t="str">
+        <x:v>Bonus type</x:v>
+      </x:c>
+      <x:c r="K6" s="51" t="str">
+        <x:v>Bonus %</x:v>
+      </x:c>
+      <x:c r="L6" s="51" t="str">
+        <x:v>Fixed reward value</x:v>
+      </x:c>
+      <x:c r="M6" s="51" t="str">
+        <x:v>Minimum deposit</x:v>
+      </x:c>
+      <x:c r="N6" s="51" t="str">
+        <x:v>Maximum bonus cap</x:v>
+      </x:c>
+      <x:c r="O6" s="51" t="str">
+        <x:v>TO requirement</x:v>
+      </x:c>
+      <x:c r="P6" s="51" t="str">
+        <x:v>Validity days</x:v>
+      </x:c>
+      <x:c r="Q6" s="51" t="str">
+        <x:v>Game / product</x:v>
+      </x:c>
+      <x:c r="R6" s="51" t="str">
+        <x:v>Code status</x:v>
+      </x:c>
+      <x:c r="S6" s="51" t="str">
+        <x:v>Confirmation needed</x:v>
+      </x:c>
+      <x:c r="T6" s="51" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+      <x:c r="U6" s="51" t="str">
+        <x:v>Received date</x:v>
+      </x:c>
+      <x:c r="V6" s="51" t="str">
+        <x:v>Exact WS1 inventory match</x:v>
+      </x:c>
+      <x:c r="W6" s="51" t="str">
+        <x:v>Matching campaign ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="52" customHeight="1">
+      <x:c r="A7" s="61" t="str">
+        <x:v>AM-KVN-002-1</x:v>
+      </x:c>
+      <x:c r="B7" s="62" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="62" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D7" s="62" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E7" s="70" t="str">
+        <x:v>Deposit bonus 20%, max bonus 300,min depo 100, TOx3</x:v>
+      </x:c>
+      <x:c r="F7" s="70" t="str">
+        <x:v>RET_ALL_20PCT_100</x:v>
+      </x:c>
+      <x:c r="G7" s="70" t="str">
+        <x:v>RET_ALL_20PCT_100</x:v>
+      </x:c>
+      <x:c r="H7" s="62" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I7" s="62" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J7" s="62" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K7" s="73" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L7" s="76"/>
+      <x:c r="M7" s="76" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N7" s="76" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="O7" s="62" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P7" s="79"/>
+      <x:c r="Q7" s="62" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R7" s="62" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S7" s="70" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T7" s="70" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U7" s="82" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V7" s="62" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W7" s="63"/>
+    </x:row>
+    <x:row r="8" ht="52" customHeight="1">
+      <x:c r="A8" s="64" t="str">
+        <x:v>AM-KVN-003-1</x:v>
+      </x:c>
+      <x:c r="B8" s="65" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D8" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E8" s="71" t="str">
+        <x:v>Deposit bonus 20%, max bonus 150,min depo 100, TOx3</x:v>
+      </x:c>
+      <x:c r="F8" s="71" t="str">
+        <x:v>REL_VIP_20PCT</x:v>
+      </x:c>
+      <x:c r="G8" s="71" t="str">
+        <x:v>REL_VIP_20PCT</x:v>
+      </x:c>
+      <x:c r="H8" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I8" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J8" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K8" s="74" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L8" s="77"/>
+      <x:c r="M8" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N8" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="O8" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P8" s="80"/>
+      <x:c r="Q8" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R8" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S8" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T8" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U8" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V8" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W8" s="66"/>
+    </x:row>
+    <x:row r="9" ht="52" customHeight="1">
+      <x:c r="A9" s="64" t="str">
+        <x:v>AM-KVN-004-1</x:v>
+      </x:c>
+      <x:c r="B9" s="65" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D9" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E9" s="71" t="str">
+        <x:v>Deposit bonus 75%, max bonus 150,min depo 100, TOx5</x:v>
+      </x:c>
+      <x:c r="F9" s="71" t="str">
+        <x:v>REL_VIP_75PCT</x:v>
+      </x:c>
+      <x:c r="G9" s="71" t="str">
+        <x:v>REL_VIP_75PCT</x:v>
+      </x:c>
+      <x:c r="H9" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I9" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J9" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K9" s="74" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="L9" s="77"/>
+      <x:c r="M9" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N9" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="O9" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P9" s="80"/>
+      <x:c r="Q9" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R9" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S9" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T9" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U9" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V9" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W9" s="66"/>
+    </x:row>
+    <x:row r="10" ht="52" customHeight="1">
+      <x:c r="A10" s="64" t="str">
+        <x:v>AM-KVN-005-1</x:v>
+      </x:c>
+      <x:c r="B10" s="65" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D10" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E10" s="71" t="str">
+        <x:v>Deposit bonus 75%, max bonus 300,min depo 100, TOx5</x:v>
+      </x:c>
+      <x:c r="F10" s="71" t="str">
+        <x:v>REL_VIP_75PCT_300MX</x:v>
+      </x:c>
+      <x:c r="G10" s="71" t="str">
+        <x:v>REL_VIP_75PCT_300MX</x:v>
+      </x:c>
+      <x:c r="H10" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I10" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J10" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K10" s="74" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="L10" s="77"/>
+      <x:c r="M10" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N10" s="77" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="O10" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P10" s="80"/>
+      <x:c r="Q10" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R10" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S10" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T10" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U10" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V10" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W10" s="66"/>
+    </x:row>
+    <x:row r="11" ht="52" customHeight="1">
+      <x:c r="A11" s="64" t="str">
+        <x:v>AM-KVN-006-1</x:v>
+      </x:c>
+      <x:c r="B11" s="65" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C11" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D11" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E11" s="71" t="str">
+        <x:v>Deposit bonus 100%, max bonus 100,min depo 100, TOx8</x:v>
+      </x:c>
+      <x:c r="F11" s="71" t="str">
+        <x:v>REL_VIP_100PCT_100MX</x:v>
+      </x:c>
+      <x:c r="G11" s="71" t="str">
+        <x:v>REL_VIP_100PCT_100MX</x:v>
+      </x:c>
+      <x:c r="H11" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I11" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J11" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K11" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L11" s="77"/>
+      <x:c r="M11" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N11" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O11" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P11" s="80"/>
+      <x:c r="Q11" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R11" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S11" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T11" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U11" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V11" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W11" s="66"/>
+    </x:row>
+    <x:row r="12" ht="52" customHeight="1">
+      <x:c r="A12" s="64" t="str">
+        <x:v>AM-KVN-007-1</x:v>
+      </x:c>
+      <x:c r="B12" s="65" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D12" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E12" s="71" t="str">
+        <x:v>Deposit bonus 100%, max bonus 250,min depo 100, TOx8</x:v>
+      </x:c>
+      <x:c r="F12" s="71" t="str">
+        <x:v>REL_VIP_100PCT_250MX</x:v>
+      </x:c>
+      <x:c r="G12" s="71" t="str">
+        <x:v>REL_VIP_100PCT_250MX</x:v>
+      </x:c>
+      <x:c r="H12" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I12" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J12" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K12" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L12" s="77"/>
+      <x:c r="M12" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N12" s="77" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="O12" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P12" s="80"/>
+      <x:c r="Q12" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R12" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S12" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T12" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U12" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V12" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W12" s="66"/>
+    </x:row>
+    <x:row r="13" ht="52" customHeight="1">
+      <x:c r="A13" s="64" t="str">
+        <x:v>AM-KVN-008-1</x:v>
+      </x:c>
+      <x:c r="B13" s="65" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D13" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E13" s="71" t="str">
+        <x:v>free credit 30 - TOx3</x:v>
+      </x:c>
+      <x:c r="F13" s="71" t="str">
+        <x:v>VIP_30FC_3X</x:v>
+      </x:c>
+      <x:c r="G13" s="71" t="str">
+        <x:v>VIP_30FC_3X</x:v>
+      </x:c>
+      <x:c r="H13" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I13" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J13" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K13" s="74"/>
+      <x:c r="L13" s="77" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M13" s="77"/>
+      <x:c r="N13" s="77"/>
+      <x:c r="O13" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P13" s="80"/>
+      <x:c r="Q13" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R13" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S13" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T13" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U13" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V13" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W13" s="66"/>
+    </x:row>
+    <x:row r="14" ht="52" customHeight="1">
+      <x:c r="A14" s="64" t="str">
+        <x:v>AM-KVN-009-1</x:v>
+      </x:c>
+      <x:c r="B14" s="65" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D14" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E14" s="71" t="str">
+        <x:v>Deposit bonus 100%/ max bonus 30/ min depo 100/ TOx3</x:v>
+      </x:c>
+      <x:c r="F14" s="71" t="str">
+        <x:v>VIP_WEL_100PCT_100_3X/ QPRO9 VIP_WELC_100PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="G14" s="71" t="str">
+        <x:v>VIP_WEL_100PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="H14" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I14" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J14" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K14" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L14" s="77"/>
+      <x:c r="M14" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N14" s="77" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O14" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P14" s="80"/>
+      <x:c r="Q14" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R14" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S14" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T14" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U14" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V14" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W14" s="66"/>
+    </x:row>
+    <x:row r="15" ht="52" customHeight="1">
+      <x:c r="A15" s="64" t="str">
+        <x:v>AM-KVN-009-2</x:v>
+      </x:c>
+      <x:c r="B15" s="65" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C15" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D15" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E15" s="71" t="str">
+        <x:v>Deposit bonus 100%/ max bonus 30/ min depo 100/ TOx3</x:v>
+      </x:c>
+      <x:c r="F15" s="71" t="str">
+        <x:v>VIP_WEL_100PCT_100_3X/ QPRO9 VIP_WELC_100PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="G15" s="71" t="str">
+        <x:v>VIP_WELC_100PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="H15" s="65" t="str">
+        <x:v>QPRO9</x:v>
+      </x:c>
+      <x:c r="I15" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J15" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K15" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L15" s="77"/>
+      <x:c r="M15" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N15" s="77" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O15" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P15" s="80"/>
+      <x:c r="Q15" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R15" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S15" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T15" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U15" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V15" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W15" s="66"/>
+    </x:row>
+    <x:row r="16" ht="52" customHeight="1">
+      <x:c r="A16" s="64" t="str">
+        <x:v>AM-KVN-010-1</x:v>
+      </x:c>
+      <x:c r="B16" s="65" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C16" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D16" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E16" s="71" t="str">
+        <x:v>Deposit bonus 50%/ max bonus 50/ min depo 100/ TOx3</x:v>
+      </x:c>
+      <x:c r="F16" s="71" t="str">
+        <x:v>VIP_WEL_50PCT_100_3X / QPRO9 VIP_WELC_50PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="G16" s="71" t="str">
+        <x:v>VIP_WEL_50PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="H16" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I16" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J16" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K16" s="74" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L16" s="77"/>
+      <x:c r="M16" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N16" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O16" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P16" s="80"/>
+      <x:c r="Q16" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R16" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S16" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T16" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U16" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V16" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W16" s="66"/>
+    </x:row>
+    <x:row r="17" ht="52" customHeight="1">
+      <x:c r="A17" s="64" t="str">
+        <x:v>AM-KVN-010-2</x:v>
+      </x:c>
+      <x:c r="B17" s="65" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C17" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D17" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E17" s="71" t="str">
+        <x:v>Deposit bonus 50%/ max bonus 50/ min depo 100/ TOx3</x:v>
+      </x:c>
+      <x:c r="F17" s="71" t="str">
+        <x:v>VIP_WEL_50PCT_100_3X / QPRO9 VIP_WELC_50PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="G17" s="71" t="str">
+        <x:v>VIP_WELC_50PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="H17" s="65" t="str">
+        <x:v>QPRO9</x:v>
+      </x:c>
+      <x:c r="I17" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J17" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K17" s="74" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L17" s="77"/>
+      <x:c r="M17" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N17" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O17" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P17" s="80"/>
+      <x:c r="Q17" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R17" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S17" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T17" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U17" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V17" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W17" s="66"/>
+    </x:row>
+    <x:row r="18" ht="52" customHeight="1">
+      <x:c r="A18" s="64" t="str">
+        <x:v>AM-KVN-011-1</x:v>
+      </x:c>
+      <x:c r="B18" s="65" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C18" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D18" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E18" s="71" t="str">
+        <x:v>free credit 50 - TOx5</x:v>
+      </x:c>
+      <x:c r="F18" s="71" t="str">
+        <x:v>VIP_50FC_5X</x:v>
+      </x:c>
+      <x:c r="G18" s="71" t="str">
+        <x:v>VIP_50FC_5X</x:v>
+      </x:c>
+      <x:c r="H18" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I18" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J18" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K18" s="74"/>
+      <x:c r="L18" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M18" s="77"/>
+      <x:c r="N18" s="77"/>
+      <x:c r="O18" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P18" s="80"/>
+      <x:c r="Q18" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R18" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S18" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T18" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U18" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V18" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W18" s="66"/>
+    </x:row>
+    <x:row r="19" ht="52" customHeight="1">
+      <x:c r="A19" s="64" t="str">
+        <x:v>AM-KVN-012-1</x:v>
+      </x:c>
+      <x:c r="B19" s="65" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C19" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D19" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E19" s="71" t="str">
+        <x:v>Deposit bonus 100%/ max bonus 50/ min depo 100/ TOx3</x:v>
+      </x:c>
+      <x:c r="F19" s="71" t="str">
+        <x:v>WELC_VIP_100PCT_50MX</x:v>
+      </x:c>
+      <x:c r="G19" s="71" t="str">
+        <x:v>WELC_VIP_100PCT_50MX</x:v>
+      </x:c>
+      <x:c r="H19" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I19" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J19" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K19" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L19" s="77"/>
+      <x:c r="M19" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N19" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O19" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P19" s="80"/>
+      <x:c r="Q19" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R19" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S19" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T19" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U19" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V19" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W19" s="66"/>
+    </x:row>
+    <x:row r="20" ht="52" customHeight="1">
+      <x:c r="A20" s="64" t="str">
+        <x:v>AM-KVN-013-1</x:v>
+      </x:c>
+      <x:c r="B20" s="65" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C20" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D20" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E20" s="71" t="str">
+        <x:v>free credit 25 - No TO</x:v>
+      </x:c>
+      <x:c r="F20" s="71" t="str">
+        <x:v>VIP_25FC_0X</x:v>
+      </x:c>
+      <x:c r="G20" s="71" t="str">
+        <x:v>VIP_25FC_0X</x:v>
+      </x:c>
+      <x:c r="H20" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I20" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J20" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K20" s="74"/>
+      <x:c r="L20" s="77" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M20" s="77"/>
+      <x:c r="N20" s="77"/>
+      <x:c r="O20" s="65" t="str">
+        <x:v>No turnover</x:v>
+      </x:c>
+      <x:c r="P20" s="80"/>
+      <x:c r="Q20" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R20" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S20" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T20" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U20" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V20" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W20" s="66"/>
+    </x:row>
+    <x:row r="21" ht="52" customHeight="1">
+      <x:c r="A21" s="64" t="str">
+        <x:v>AM-KVN-014-1</x:v>
+      </x:c>
+      <x:c r="B21" s="65" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D21" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E21" s="71" t="str">
+        <x:v>free credit 30 - TOx5</x:v>
+      </x:c>
+      <x:c r="F21" s="71" t="str">
+        <x:v>VIP_30FC_5X</x:v>
+      </x:c>
+      <x:c r="G21" s="71" t="str">
+        <x:v>VIP_30FC_5X</x:v>
+      </x:c>
+      <x:c r="H21" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I21" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J21" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K21" s="74"/>
+      <x:c r="L21" s="77" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M21" s="77"/>
+      <x:c r="N21" s="77"/>
+      <x:c r="O21" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P21" s="80"/>
+      <x:c r="Q21" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R21" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S21" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T21" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U21" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V21" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W21" s="66"/>
+    </x:row>
+    <x:row r="22" ht="52" customHeight="1">
+      <x:c r="A22" s="64" t="str">
+        <x:v>AM-KVN-015-1</x:v>
+      </x:c>
+      <x:c r="B22" s="65" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C22" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D22" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E22" s="71" t="str">
+        <x:v>Deposit bonus 75%/ max bonus 60/ min depo 100/ TOx5</x:v>
+      </x:c>
+      <x:c r="F22" s="71" t="str">
+        <x:v>WELC_VIP_75PCT_60MX</x:v>
+      </x:c>
+      <x:c r="G22" s="71" t="str">
+        <x:v>WELC_VIP_75PCT_60MX</x:v>
+      </x:c>
+      <x:c r="H22" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I22" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J22" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K22" s="74" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="L22" s="77"/>
+      <x:c r="M22" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N22" s="77" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="O22" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P22" s="80"/>
+      <x:c r="Q22" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R22" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S22" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T22" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U22" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V22" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W22" s="66"/>
+    </x:row>
+    <x:row r="23" ht="52" customHeight="1">
+      <x:c r="A23" s="64" t="str">
+        <x:v>AM-KVN-016-1</x:v>
+      </x:c>
+      <x:c r="B23" s="65" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C23" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D23" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E23" s="71" t="str">
+        <x:v>Deposit bonus 50%/ max bonus 50/ min depo 100/ TOx5</x:v>
+      </x:c>
+      <x:c r="F23" s="71" t="str">
+        <x:v>WELC_VIP_50PCT_50MX</x:v>
+      </x:c>
+      <x:c r="G23" s="71" t="str">
+        <x:v>WELC_VIP_50PCT_50MX</x:v>
+      </x:c>
+      <x:c r="H23" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I23" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J23" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K23" s="74" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L23" s="77"/>
+      <x:c r="M23" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N23" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O23" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P23" s="80"/>
+      <x:c r="Q23" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R23" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S23" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T23" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U23" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V23" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W23" s="66"/>
+    </x:row>
+    <x:row r="24" ht="52" customHeight="1">
+      <x:c r="A24" s="64" t="str">
+        <x:v>AM-KVN-017-1</x:v>
+      </x:c>
+      <x:c r="B24" s="65" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C24" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D24" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E24" s="71" t="str">
+        <x:v>Deposit bonus 75%/ max bonus 100 / min depo 100/ TOx5</x:v>
+      </x:c>
+      <x:c r="F24" s="71" t="str">
+        <x:v>WELC_VIP_75PCT_100MX</x:v>
+      </x:c>
+      <x:c r="G24" s="71" t="str">
+        <x:v>WELC_VIP_75PCT_100MX</x:v>
+      </x:c>
+      <x:c r="H24" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I24" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J24" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K24" s="74" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="L24" s="77"/>
+      <x:c r="M24" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N24" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O24" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P24" s="80"/>
+      <x:c r="Q24" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R24" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S24" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T24" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U24" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V24" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W24" s="66"/>
+    </x:row>
+    <x:row r="25" ht="52" customHeight="1">
+      <x:c r="A25" s="64" t="str">
+        <x:v>AM-KVN-018-1</x:v>
+      </x:c>
+      <x:c r="B25" s="65" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C25" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D25" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E25" s="71" t="str">
+        <x:v>Deposit bonus 50%/ max bonus 30/ min depo 100/ TOx3</x:v>
+      </x:c>
+      <x:c r="F25" s="71" t="str">
+        <x:v>WELC_VIP_50PCT_30MX</x:v>
+      </x:c>
+      <x:c r="G25" s="71" t="str">
+        <x:v>WELC_VIP_50PCT_30MX</x:v>
+      </x:c>
+      <x:c r="H25" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I25" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J25" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K25" s="74" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L25" s="77"/>
+      <x:c r="M25" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N25" s="77" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O25" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P25" s="80"/>
+      <x:c r="Q25" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R25" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S25" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T25" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U25" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V25" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W25" s="66"/>
+    </x:row>
+    <x:row r="26" ht="52" customHeight="1">
+      <x:c r="A26" s="64" t="str">
+        <x:v>AM-KVN-019-1</x:v>
+      </x:c>
+      <x:c r="B26" s="65" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C26" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D26" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E26" s="71" t="str">
+        <x:v>free credit 15- No TO</x:v>
+      </x:c>
+      <x:c r="F26" s="71" t="str">
+        <x:v>VIP_15FC_0X</x:v>
+      </x:c>
+      <x:c r="G26" s="71" t="str">
+        <x:v>VIP_15FC_0X</x:v>
+      </x:c>
+      <x:c r="H26" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I26" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J26" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K26" s="74"/>
+      <x:c r="L26" s="77" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M26" s="77"/>
+      <x:c r="N26" s="77"/>
+      <x:c r="O26" s="65" t="str">
+        <x:v>No turnover</x:v>
+      </x:c>
+      <x:c r="P26" s="80"/>
+      <x:c r="Q26" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R26" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S26" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T26" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U26" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V26" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W26" s="66"/>
+    </x:row>
+    <x:row r="27" ht="52" customHeight="1">
+      <x:c r="A27" s="64" t="str">
+        <x:v>AM-KVN-020-1</x:v>
+      </x:c>
+      <x:c r="B27" s="65" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C27" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D27" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E27" s="71" t="str">
+        <x:v>free credit 30- TOx10</x:v>
+      </x:c>
+      <x:c r="F27" s="71"/>
+      <x:c r="G27" s="71"/>
+      <x:c r="H27" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I27" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J27" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K27" s="74"/>
+      <x:c r="L27" s="77" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M27" s="77"/>
+      <x:c r="N27" s="77"/>
+      <x:c r="O27" s="65" t="str">
+        <x:v>10x</x:v>
+      </x:c>
+      <x:c r="P27" s="80"/>
+      <x:c r="Q27" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R27" s="65" t="str">
+        <x:v>Missing</x:v>
+      </x:c>
+      <x:c r="S27" s="71" t="str">
+        <x:v>Promo code is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T27" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U27" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V27" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W27" s="66"/>
+    </x:row>
+    <x:row r="28" ht="52" customHeight="1">
+      <x:c r="A28" s="64" t="str">
+        <x:v>AM-KVN-021-1</x:v>
+      </x:c>
+      <x:c r="B28" s="65" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C28" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D28" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E28" s="71" t="str">
+        <x:v>Deposit bonus 30%/ max bonus 150/ min depo 500/ TOx3</x:v>
+      </x:c>
+      <x:c r="F28" s="71" t="str">
+        <x:v>VIP_30PCT_150MX_3X / FT_VIP_30PCT_150MX_3X</x:v>
+      </x:c>
+      <x:c r="G28" s="71" t="str">
+        <x:v>VIP_30PCT_150MX_3X</x:v>
+      </x:c>
+      <x:c r="H28" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I28" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J28" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K28" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L28" s="77"/>
+      <x:c r="M28" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="N28" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="O28" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P28" s="80"/>
+      <x:c r="Q28" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R28" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S28" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T28" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U28" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V28" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W28" s="66"/>
+    </x:row>
+    <x:row r="29" ht="52" customHeight="1">
+      <x:c r="A29" s="64" t="str">
+        <x:v>AM-KVN-021-2</x:v>
+      </x:c>
+      <x:c r="B29" s="65" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C29" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D29" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E29" s="71" t="str">
+        <x:v>Deposit bonus 30%/ max bonus 150/ min depo 500/ TOx3</x:v>
+      </x:c>
+      <x:c r="F29" s="71" t="str">
+        <x:v>VIP_30PCT_150MX_3X / FT_VIP_30PCT_150MX_3X</x:v>
+      </x:c>
+      <x:c r="G29" s="71" t="str">
+        <x:v>FT_VIP_30PCT_150MX_3X</x:v>
+      </x:c>
+      <x:c r="H29" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I29" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J29" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K29" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L29" s="77"/>
+      <x:c r="M29" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="N29" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="O29" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P29" s="80"/>
+      <x:c r="Q29" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R29" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S29" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T29" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U29" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V29" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W29" s="66"/>
+    </x:row>
+    <x:row r="30" ht="52" customHeight="1">
+      <x:c r="A30" s="64" t="str">
+        <x:v>AM-KVN-022-1</x:v>
+      </x:c>
+      <x:c r="B30" s="65" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C30" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D30" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E30" s="71" t="str">
+        <x:v>Deposit bonus 20%/ max bonus 10/ min depo 50/ TOx3</x:v>
+      </x:c>
+      <x:c r="F30" s="71" t="str">
+        <x:v>VIP_20PCT_10MX_3X/ FT_VIP_20PCT_50_3X</x:v>
+      </x:c>
+      <x:c r="G30" s="71" t="str">
+        <x:v>VIP_20PCT_10MX_3X</x:v>
+      </x:c>
+      <x:c r="H30" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I30" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J30" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K30" s="74" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L30" s="77"/>
+      <x:c r="M30" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N30" s="77" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O30" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P30" s="80"/>
+      <x:c r="Q30" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R30" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S30" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T30" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U30" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V30" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W30" s="66"/>
+    </x:row>
+    <x:row r="31" ht="52" customHeight="1">
+      <x:c r="A31" s="64" t="str">
+        <x:v>AM-KVN-022-2</x:v>
+      </x:c>
+      <x:c r="B31" s="65" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C31" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D31" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E31" s="71" t="str">
+        <x:v>Deposit bonus 20%/ max bonus 10/ min depo 50/ TOx3</x:v>
+      </x:c>
+      <x:c r="F31" s="71" t="str">
+        <x:v>VIP_20PCT_10MX_3X/ FT_VIP_20PCT_50_3X</x:v>
+      </x:c>
+      <x:c r="G31" s="71" t="str">
+        <x:v>FT_VIP_20PCT_50_3X</x:v>
+      </x:c>
+      <x:c r="H31" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I31" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J31" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K31" s="74" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L31" s="77"/>
+      <x:c r="M31" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N31" s="77" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O31" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P31" s="80"/>
+      <x:c r="Q31" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R31" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S31" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T31" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U31" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V31" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W31" s="66"/>
+    </x:row>
+    <x:row r="32" ht="52" customHeight="1">
+      <x:c r="A32" s="64" t="str">
+        <x:v>AM-KVN-023-1</x:v>
+      </x:c>
+      <x:c r="B32" s="65" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C32" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D32" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E32" s="71" t="str">
+        <x:v>Deposit bonus 25%/ max bonus 50/ min depo 200/ TOx3</x:v>
+      </x:c>
+      <x:c r="F32" s="71" t="str">
+        <x:v>VIP_25PCT_50MX_3X/ FT_VIP_25PCT_200_3X</x:v>
+      </x:c>
+      <x:c r="G32" s="71" t="str">
+        <x:v>VIP_25PCT_50MX_3X</x:v>
+      </x:c>
+      <x:c r="H32" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I32" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J32" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K32" s="74" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="L32" s="77"/>
+      <x:c r="M32" s="77" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="N32" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O32" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P32" s="80"/>
+      <x:c r="Q32" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R32" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S32" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T32" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U32" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V32" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W32" s="66"/>
+    </x:row>
+    <x:row r="33" ht="52" customHeight="1">
+      <x:c r="A33" s="64" t="str">
+        <x:v>AM-KVN-023-2</x:v>
+      </x:c>
+      <x:c r="B33" s="65" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C33" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D33" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E33" s="71" t="str">
+        <x:v>Deposit bonus 25%/ max bonus 50/ min depo 200/ TOx3</x:v>
+      </x:c>
+      <x:c r="F33" s="71" t="str">
+        <x:v>VIP_25PCT_50MX_3X/ FT_VIP_25PCT_200_3X</x:v>
+      </x:c>
+      <x:c r="G33" s="71" t="str">
+        <x:v>FT_VIP_25PCT_200_3X</x:v>
+      </x:c>
+      <x:c r="H33" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I33" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J33" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K33" s="74" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="L33" s="77"/>
+      <x:c r="M33" s="77" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="N33" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O33" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P33" s="80"/>
+      <x:c r="Q33" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R33" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S33" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T33" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U33" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V33" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W33" s="66"/>
+    </x:row>
+    <x:row r="34" ht="52" customHeight="1">
+      <x:c r="A34" s="64" t="str">
+        <x:v>AM-KVN-024-1</x:v>
+      </x:c>
+      <x:c r="B34" s="65" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C34" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D34" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E34" s="71" t="str">
+        <x:v>Deposit bonus 20%/ max bonus 20/ min depo 100/ TOx3</x:v>
+      </x:c>
+      <x:c r="F34" s="71" t="str">
+        <x:v>VIP_20PCT_20MX_3X / FT_VIP_20PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="G34" s="71" t="str">
+        <x:v>VIP_20PCT_20MX_3X</x:v>
+      </x:c>
+      <x:c r="H34" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I34" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J34" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K34" s="74" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L34" s="77"/>
+      <x:c r="M34" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N34" s="77" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O34" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P34" s="80"/>
+      <x:c r="Q34" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R34" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S34" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T34" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U34" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V34" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W34" s="66"/>
+    </x:row>
+    <x:row r="35" ht="52" customHeight="1">
+      <x:c r="A35" s="64" t="str">
+        <x:v>AM-KVN-024-2</x:v>
+      </x:c>
+      <x:c r="B35" s="65" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C35" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D35" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E35" s="71" t="str">
+        <x:v>Deposit bonus 20%/ max bonus 20/ min depo 100/ TOx3</x:v>
+      </x:c>
+      <x:c r="F35" s="71" t="str">
+        <x:v>VIP_20PCT_20MX_3X / FT_VIP_20PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="G35" s="71" t="str">
+        <x:v>FT_VIP_20PCT_100_3X</x:v>
+      </x:c>
+      <x:c r="H35" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I35" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J35" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K35" s="74" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L35" s="77"/>
+      <x:c r="M35" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N35" s="77" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O35" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P35" s="80"/>
+      <x:c r="Q35" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R35" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S35" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T35" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U35" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V35" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W35" s="66"/>
+    </x:row>
+    <x:row r="36" ht="52" customHeight="1">
+      <x:c r="A36" s="64" t="str">
+        <x:v>AM-KVN-025-1</x:v>
+      </x:c>
+      <x:c r="B36" s="65" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C36" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D36" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E36" s="71" t="str">
+        <x:v>Deposit bonus 50%/ max bonus 500/ min depo 1000/ TOx3</x:v>
+      </x:c>
+      <x:c r="F36" s="71" t="str">
+        <x:v>VIP_50PCT_500MX_3X / FT_VIP_50PCT_1000_3X</x:v>
+      </x:c>
+      <x:c r="G36" s="71" t="str">
+        <x:v>VIP_50PCT_500MX_3X</x:v>
+      </x:c>
+      <x:c r="H36" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I36" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J36" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K36" s="74" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L36" s="77"/>
+      <x:c r="M36" s="77" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N36" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O36" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P36" s="80"/>
+      <x:c r="Q36" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R36" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S36" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T36" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U36" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V36" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W36" s="66"/>
+    </x:row>
+    <x:row r="37" ht="52" customHeight="1">
+      <x:c r="A37" s="64" t="str">
+        <x:v>AM-KVN-025-2</x:v>
+      </x:c>
+      <x:c r="B37" s="65" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C37" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D37" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E37" s="71" t="str">
+        <x:v>Deposit bonus 50%/ max bonus 500/ min depo 1000/ TOx3</x:v>
+      </x:c>
+      <x:c r="F37" s="71" t="str">
+        <x:v>VIP_50PCT_500MX_3X / FT_VIP_50PCT_1000_3X</x:v>
+      </x:c>
+      <x:c r="G37" s="71" t="str">
+        <x:v>FT_VIP_50PCT_1000_3X</x:v>
+      </x:c>
+      <x:c r="H37" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I37" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J37" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K37" s="74" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L37" s="77"/>
+      <x:c r="M37" s="77" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N37" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O37" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P37" s="80"/>
+      <x:c r="Q37" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R37" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S37" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T37" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U37" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V37" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W37" s="66"/>
+    </x:row>
+    <x:row r="38" ht="52" customHeight="1">
+      <x:c r="A38" s="64" t="str">
+        <x:v>AM-KVN-026-1</x:v>
+      </x:c>
+      <x:c r="B38" s="65" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C38" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D38" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E38" s="71" t="str">
+        <x:v>Deposit bonus 50%/ max bonus 150/ min depo 300/ TOx3</x:v>
+      </x:c>
+      <x:c r="F38" s="71" t="str">
+        <x:v>VIP_50PCT_150MX_3X / FT_VIP_50PCT_150MX_3X</x:v>
+      </x:c>
+      <x:c r="G38" s="71" t="str">
+        <x:v>VIP_50PCT_150MX_3X</x:v>
+      </x:c>
+      <x:c r="H38" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I38" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J38" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K38" s="74" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L38" s="77"/>
+      <x:c r="M38" s="77" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="N38" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="O38" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P38" s="80"/>
+      <x:c r="Q38" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R38" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S38" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T38" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U38" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V38" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W38" s="66"/>
+    </x:row>
+    <x:row r="39" ht="52" customHeight="1">
+      <x:c r="A39" s="64" t="str">
+        <x:v>AM-KVN-026-2</x:v>
+      </x:c>
+      <x:c r="B39" s="65" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C39" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D39" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E39" s="71" t="str">
+        <x:v>Deposit bonus 50%/ max bonus 150/ min depo 300/ TOx3</x:v>
+      </x:c>
+      <x:c r="F39" s="71" t="str">
+        <x:v>VIP_50PCT_150MX_3X / FT_VIP_50PCT_150MX_3X</x:v>
+      </x:c>
+      <x:c r="G39" s="71" t="str">
+        <x:v>FT_VIP_50PCT_150MX_3X</x:v>
+      </x:c>
+      <x:c r="H39" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I39" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J39" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K39" s="74" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L39" s="77"/>
+      <x:c r="M39" s="77" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="N39" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="O39" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P39" s="80"/>
+      <x:c r="Q39" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R39" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S39" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T39" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U39" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V39" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W39" s="66"/>
+    </x:row>
+    <x:row r="40" ht="52" customHeight="1">
+      <x:c r="A40" s="64" t="str">
+        <x:v>AM-KVN-027-1</x:v>
+      </x:c>
+      <x:c r="B40" s="65" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C40" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D40" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E40" s="71" t="str">
+        <x:v>Deposit bonus 30%/ max bonus 45/ min depo 150/ TOx3</x:v>
+      </x:c>
+      <x:c r="F40" s="71" t="str">
+        <x:v>VIP_30PCT_45MX_3X/ FT_VIP_30PCT_45MX_3X</x:v>
+      </x:c>
+      <x:c r="G40" s="71" t="str">
+        <x:v>VIP_30PCT_45MX_3X</x:v>
+      </x:c>
+      <x:c r="H40" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I40" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J40" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K40" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L40" s="77"/>
+      <x:c r="M40" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="N40" s="77" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O40" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P40" s="80"/>
+      <x:c r="Q40" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R40" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S40" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T40" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U40" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V40" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W40" s="66"/>
+    </x:row>
+    <x:row r="41" ht="52" customHeight="1">
+      <x:c r="A41" s="64" t="str">
+        <x:v>AM-KVN-027-2</x:v>
+      </x:c>
+      <x:c r="B41" s="65" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C41" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D41" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E41" s="71" t="str">
+        <x:v>Deposit bonus 30%/ max bonus 45/ min depo 150/ TOx3</x:v>
+      </x:c>
+      <x:c r="F41" s="71" t="str">
+        <x:v>VIP_30PCT_45MX_3X/ FT_VIP_30PCT_45MX_3X</x:v>
+      </x:c>
+      <x:c r="G41" s="71" t="str">
+        <x:v>FT_VIP_30PCT_45MX_3X</x:v>
+      </x:c>
+      <x:c r="H41" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I41" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J41" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K41" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L41" s="77"/>
+      <x:c r="M41" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="N41" s="77" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O41" s="65" t="str">
+        <x:v>3x</x:v>
+      </x:c>
+      <x:c r="P41" s="80"/>
+      <x:c r="Q41" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R41" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S41" s="71" t="str">
+        <x:v>Confirm the mapping for codes supplied in one cell; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T41" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U41" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V41" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W41" s="66"/>
+    </x:row>
+    <x:row r="42" ht="52" customHeight="1">
+      <x:c r="A42" s="64" t="str">
+        <x:v>AM-KVN-028-1</x:v>
+      </x:c>
+      <x:c r="B42" s="65" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C42" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D42" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E42" s="71" t="str">
+        <x:v>100% Slots/Fishing reload, min RM 1,000, cap RM 500, 5x TO</x:v>
+      </x:c>
+      <x:c r="F42" s="71" t="str">
+        <x:v>VIP_REL_100PCT_MIN1000_5X</x:v>
+      </x:c>
+      <x:c r="G42" s="71" t="str">
+        <x:v>VIP_REL_100PCT_MIN1000_5X</x:v>
+      </x:c>
+      <x:c r="H42" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I42" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J42" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K42" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L42" s="77"/>
+      <x:c r="M42" s="77" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N42" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O42" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P42" s="80"/>
+      <x:c r="Q42" s="65" t="str">
+        <x:v>Slots / Fishing</x:v>
+      </x:c>
+      <x:c r="R42" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S42" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T42" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U42" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V42" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W42" s="66"/>
+    </x:row>
+    <x:row r="43" ht="52" customHeight="1">
+      <x:c r="A43" s="64" t="str">
+        <x:v>AM-KVN-029-1</x:v>
+      </x:c>
+      <x:c r="B43" s="65" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C43" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D43" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E43" s="71" t="str">
+        <x:v>100% Slots/Fishing reload, min RM 1,500, cap RM 500, 5x TO</x:v>
+      </x:c>
+      <x:c r="F43" s="71" t="str">
+        <x:v>VIP_REL_100PCT_MIN1500_5X</x:v>
+      </x:c>
+      <x:c r="G43" s="71" t="str">
+        <x:v>VIP_REL_100PCT_MIN1500_5X</x:v>
+      </x:c>
+      <x:c r="H43" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I43" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J43" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K43" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L43" s="77"/>
+      <x:c r="M43" s="77" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="N43" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O43" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P43" s="80"/>
+      <x:c r="Q43" s="65" t="str">
+        <x:v>Slots / Fishing</x:v>
+      </x:c>
+      <x:c r="R43" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S43" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T43" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U43" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V43" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W43" s="66"/>
+    </x:row>
+    <x:row r="44" ht="52" customHeight="1">
+      <x:c r="A44" s="64" t="str">
+        <x:v>AM-KVN-030-1</x:v>
+      </x:c>
+      <x:c r="B44" s="65" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C44" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D44" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E44" s="71" t="str">
+        <x:v>100% Slots/Fishing reload, min RM 2,000, cap RM 500, 5x TO</x:v>
+      </x:c>
+      <x:c r="F44" s="71" t="str">
+        <x:v>VIP_REL_100PCT_MIN2000_5X</x:v>
+      </x:c>
+      <x:c r="G44" s="71" t="str">
+        <x:v>VIP_REL_100PCT_MIN2000_5X</x:v>
+      </x:c>
+      <x:c r="H44" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I44" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J44" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K44" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L44" s="77"/>
+      <x:c r="M44" s="77" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="N44" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O44" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P44" s="80"/>
+      <x:c r="Q44" s="65" t="str">
+        <x:v>Slots / Fishing</x:v>
+      </x:c>
+      <x:c r="R44" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S44" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T44" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U44" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V44" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W44" s="66"/>
+    </x:row>
+    <x:row r="45" ht="52" customHeight="1">
+      <x:c r="A45" s="64" t="str">
+        <x:v>AM-KVN-031-1</x:v>
+      </x:c>
+      <x:c r="B45" s="65" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C45" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D45" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E45" s="71" t="str">
+        <x:v>100% Slots/Fishing reload, min RM 3,000, cap RM 500, 5x TO</x:v>
+      </x:c>
+      <x:c r="F45" s="71" t="str">
+        <x:v>VIP_REL_100PCT_MIN3000_5X</x:v>
+      </x:c>
+      <x:c r="G45" s="71" t="str">
+        <x:v>VIP_REL_100PCT_MIN3000_5X</x:v>
+      </x:c>
+      <x:c r="H45" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I45" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J45" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K45" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L45" s="77"/>
+      <x:c r="M45" s="77" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="N45" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O45" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P45" s="80"/>
+      <x:c r="Q45" s="65" t="str">
+        <x:v>Slots / Fishing</x:v>
+      </x:c>
+      <x:c r="R45" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S45" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T45" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U45" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V45" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W45" s="66"/>
+    </x:row>
+    <x:row r="46" ht="52" customHeight="1">
+      <x:c r="A46" s="64" t="str">
+        <x:v>AM-KVN-032-1</x:v>
+      </x:c>
+      <x:c r="B46" s="65" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C46" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D46" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E46" s="71" t="str">
+        <x:v>30% All Games reload, min RM 1,000, cap RM 600, 8x TO</x:v>
+      </x:c>
+      <x:c r="F46" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN1000_8X</x:v>
+      </x:c>
+      <x:c r="G46" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN1000_8X</x:v>
+      </x:c>
+      <x:c r="H46" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I46" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J46" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K46" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L46" s="77"/>
+      <x:c r="M46" s="77" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N46" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O46" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P46" s="80"/>
+      <x:c r="Q46" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R46" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S46" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T46" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U46" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V46" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W46" s="66"/>
+    </x:row>
+    <x:row r="47" ht="52" customHeight="1">
+      <x:c r="A47" s="64" t="str">
+        <x:v>AM-KVN-033-1</x:v>
+      </x:c>
+      <x:c r="B47" s="65" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C47" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D47" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E47" s="71" t="str">
+        <x:v>30% All Games reload, min RM 1,500, cap RM 600, 8x TO</x:v>
+      </x:c>
+      <x:c r="F47" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN1500_8X</x:v>
+      </x:c>
+      <x:c r="G47" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN1500_8X</x:v>
+      </x:c>
+      <x:c r="H47" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I47" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J47" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K47" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L47" s="77"/>
+      <x:c r="M47" s="77" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="N47" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O47" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P47" s="80"/>
+      <x:c r="Q47" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R47" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S47" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T47" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U47" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V47" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W47" s="66"/>
+    </x:row>
+    <x:row r="48" ht="52" customHeight="1">
+      <x:c r="A48" s="64" t="str">
+        <x:v>AM-KVN-034-1</x:v>
+      </x:c>
+      <x:c r="B48" s="65" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C48" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D48" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E48" s="71" t="str">
+        <x:v>30% All Games reload, min RM 2,000, cap RM 600, 8x TO</x:v>
+      </x:c>
+      <x:c r="F48" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN2000_8X</x:v>
+      </x:c>
+      <x:c r="G48" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN2000_8X</x:v>
+      </x:c>
+      <x:c r="H48" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I48" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J48" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K48" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L48" s="77"/>
+      <x:c r="M48" s="77" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="N48" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O48" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P48" s="80"/>
+      <x:c r="Q48" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R48" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S48" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T48" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U48" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V48" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W48" s="66"/>
+    </x:row>
+    <x:row r="49" ht="52" customHeight="1">
+      <x:c r="A49" s="64" t="str">
+        <x:v>AM-KVN-035-1</x:v>
+      </x:c>
+      <x:c r="B49" s="65" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C49" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D49" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E49" s="71" t="str">
+        <x:v>30% All Games reload, min RM 3,500, cap RM 600, 8x TO</x:v>
+      </x:c>
+      <x:c r="F49" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN3500_8X</x:v>
+      </x:c>
+      <x:c r="G49" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN3500_8X</x:v>
+      </x:c>
+      <x:c r="H49" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I49" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J49" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K49" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L49" s="77"/>
+      <x:c r="M49" s="77" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+      <x:c r="N49" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O49" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P49" s="80"/>
+      <x:c r="Q49" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R49" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S49" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T49" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U49" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V49" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W49" s="66"/>
+    </x:row>
+    <x:row r="50" ht="52" customHeight="1">
+      <x:c r="A50" s="64" t="str">
+        <x:v>AM-KVN-036-1</x:v>
+      </x:c>
+      <x:c r="B50" s="65" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C50" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D50" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E50" s="71" t="str">
+        <x:v>30% All Games reload, min RM 4,000, cap RM 600, 8x TO</x:v>
+      </x:c>
+      <x:c r="F50" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN4000_8X</x:v>
+      </x:c>
+      <x:c r="G50" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN4000_8X</x:v>
+      </x:c>
+      <x:c r="H50" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I50" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J50" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K50" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L50" s="77"/>
+      <x:c r="M50" s="77" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="N50" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O50" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P50" s="80"/>
+      <x:c r="Q50" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R50" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S50" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T50" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U50" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V50" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W50" s="66"/>
+    </x:row>
+    <x:row r="51" ht="52" customHeight="1">
+      <x:c r="A51" s="64" t="str">
+        <x:v>AM-KVN-037-1</x:v>
+      </x:c>
+      <x:c r="B51" s="65" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C51" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D51" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E51" s="71" t="str">
+        <x:v>30% All Games reload, min RM 6,500, cap RM 600, 8x TO</x:v>
+      </x:c>
+      <x:c r="F51" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN6500_8X</x:v>
+      </x:c>
+      <x:c r="G51" s="71" t="str">
+        <x:v>VIP_REL_30PCT_MIN6500_8X</x:v>
+      </x:c>
+      <x:c r="H51" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I51" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J51" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K51" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L51" s="77"/>
+      <x:c r="M51" s="77" t="n">
+        <x:v>6500</x:v>
+      </x:c>
+      <x:c r="N51" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O51" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P51" s="80"/>
+      <x:c r="Q51" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R51" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S51" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T51" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U51" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V51" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W51" s="66"/>
+    </x:row>
+    <x:row r="52" ht="52" customHeight="1">
+      <x:c r="A52" s="64" t="str">
+        <x:v>AM-KVN-038-1</x:v>
+      </x:c>
+      <x:c r="B52" s="65" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C52" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D52" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E52" s="71" t="str">
+        <x:v>Deposit bonus 30%/ max bonus 600/ min depo 3000/ TOx8 Game : All games</x:v>
+      </x:c>
+      <x:c r="F52" s="71" t="str">
+        <x:v>VIP_REL_30PCT_8X_MIN3000</x:v>
+      </x:c>
+      <x:c r="G52" s="71" t="str">
+        <x:v>VIP_REL_30PCT_8X_MIN3000</x:v>
+      </x:c>
+      <x:c r="H52" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I52" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J52" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K52" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L52" s="77"/>
+      <x:c r="M52" s="77" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="N52" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O52" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P52" s="80"/>
+      <x:c r="Q52" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R52" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S52" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T52" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U52" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V52" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W52" s="66"/>
+    </x:row>
+    <x:row r="53" ht="52" customHeight="1">
+      <x:c r="A53" s="64" t="str">
+        <x:v>AM-KVN-039-1</x:v>
+      </x:c>
+      <x:c r="B53" s="65" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C53" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D53" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E53" s="71" t="str">
+        <x:v>Deposit bonus 30%/ max bonus 600/ min depo 6000/ TOx8 Game : All games</x:v>
+      </x:c>
+      <x:c r="F53" s="71" t="str">
+        <x:v>VIP_REL_30PCT_8X_MIN6000</x:v>
+      </x:c>
+      <x:c r="G53" s="71" t="str">
+        <x:v>VIP_REL_30PCT_8X_MIN6000</x:v>
+      </x:c>
+      <x:c r="H53" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I53" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J53" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K53" s="74" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="L53" s="77"/>
+      <x:c r="M53" s="77" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="N53" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="O53" s="65" t="str">
+        <x:v>8x</x:v>
+      </x:c>
+      <x:c r="P53" s="80"/>
+      <x:c r="Q53" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R53" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S53" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T53" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U53" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V53" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W53" s="66"/>
+    </x:row>
+    <x:row r="54" ht="52" customHeight="1">
+      <x:c r="A54" s="64" t="str">
+        <x:v>AM-KVN-040-1</x:v>
+      </x:c>
+      <x:c r="B54" s="65" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C54" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D54" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E54" s="71" t="str">
+        <x:v>Deposit bonus 100%/ max bonus 500/ min depo 2500/ TOx5 Game Categories : Slots/Fishing reload</x:v>
+      </x:c>
+      <x:c r="F54" s="71" t="str">
+        <x:v>VIP_REL_100PCT_5X_MIN2500</x:v>
+      </x:c>
+      <x:c r="G54" s="71" t="str">
+        <x:v>VIP_REL_100PCT_5X_MIN2500</x:v>
+      </x:c>
+      <x:c r="H54" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I54" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J54" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K54" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L54" s="77"/>
+      <x:c r="M54" s="77" t="n">
+        <x:v>2500</x:v>
+      </x:c>
+      <x:c r="N54" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O54" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P54" s="80"/>
+      <x:c r="Q54" s="65" t="str">
+        <x:v>Slots / Fishing</x:v>
+      </x:c>
+      <x:c r="R54" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S54" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T54" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U54" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V54" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W54" s="66"/>
+    </x:row>
+    <x:row r="55" ht="52" customHeight="1">
+      <x:c r="A55" s="64" t="str">
+        <x:v>AM-KVN-041-1</x:v>
+      </x:c>
+      <x:c r="B55" s="65" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C55" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D55" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E55" s="71" t="str">
+        <x:v>Deposit bonus 100%/ max bonus 500/ min depo 3500/ TOx5 Game Categories : Slots/Fishing reload</x:v>
+      </x:c>
+      <x:c r="F55" s="71" t="str">
+        <x:v>VIP_REL_100PCT_5X_MIN3500</x:v>
+      </x:c>
+      <x:c r="G55" s="71" t="str">
+        <x:v>VIP_REL_100PCT_5X_MIN3500</x:v>
+      </x:c>
+      <x:c r="H55" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I55" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J55" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K55" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L55" s="77"/>
+      <x:c r="M55" s="77" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+      <x:c r="N55" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O55" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P55" s="80"/>
+      <x:c r="Q55" s="65" t="str">
+        <x:v>Slots / Fishing</x:v>
+      </x:c>
+      <x:c r="R55" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S55" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T55" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U55" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V55" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W55" s="66"/>
+    </x:row>
+    <x:row r="56" ht="52" customHeight="1">
+      <x:c r="A56" s="64" t="str">
+        <x:v>AM-KVN-042-1</x:v>
+      </x:c>
+      <x:c r="B56" s="65" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C56" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D56" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E56" s="71" t="str">
+        <x:v>Deposit bonus 100%/ max bonus 500/ min depo 4000/ TOx5 Game Categories : Slots/Fishing reload</x:v>
+      </x:c>
+      <x:c r="F56" s="71" t="str">
+        <x:v>VIP_REL_100PCT_5X_MIN4000</x:v>
+      </x:c>
+      <x:c r="G56" s="71" t="str">
+        <x:v>VIP_REL_100PCT_5X_MIN4000</x:v>
+      </x:c>
+      <x:c r="H56" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I56" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J56" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K56" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L56" s="77"/>
+      <x:c r="M56" s="77" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="N56" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O56" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P56" s="80"/>
+      <x:c r="Q56" s="65" t="str">
+        <x:v>Slots / Fishing</x:v>
+      </x:c>
+      <x:c r="R56" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S56" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T56" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U56" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V56" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W56" s="66"/>
+    </x:row>
+    <x:row r="57" ht="52" customHeight="1">
+      <x:c r="A57" s="64" t="str">
+        <x:v>AM-KVN-043-1</x:v>
+      </x:c>
+      <x:c r="B57" s="65" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C57" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D57" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E57" s="71" t="str">
+        <x:v>Deposit bonus 100%/ max bonus 500/ min depo 8500/ TOx5 Game Categories : Slots/Fishing reload</x:v>
+      </x:c>
+      <x:c r="F57" s="71" t="str">
+        <x:v>VIP_REL_100PCT_5X_MIN8500</x:v>
+      </x:c>
+      <x:c r="G57" s="71" t="str">
+        <x:v>VIP_REL_100PCT_5X_MIN8500</x:v>
+      </x:c>
+      <x:c r="H57" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I57" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J57" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K57" s="74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L57" s="77"/>
+      <x:c r="M57" s="77" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="N57" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O57" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P57" s="80"/>
+      <x:c r="Q57" s="65" t="str">
+        <x:v>Slots / Fishing</x:v>
+      </x:c>
+      <x:c r="R57" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S57" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T57" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U57" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V57" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W57" s="66"/>
+    </x:row>
+    <x:row r="58" ht="52" customHeight="1">
+      <x:c r="A58" s="64" t="str">
+        <x:v>AM-KVN-044-1</x:v>
+      </x:c>
+      <x:c r="B58" s="65" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C58" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D58" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E58" s="71" t="str">
+        <x:v>30 Free Credits, TO 5, (All Games)</x:v>
+      </x:c>
+      <x:c r="F58" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="G58" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="H58" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I58" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J58" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K58" s="74"/>
+      <x:c r="L58" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M58" s="77"/>
+      <x:c r="N58" s="77"/>
+      <x:c r="O58" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P58" s="80"/>
+      <x:c r="Q58" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R58" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S58" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm shared or variable mechanics for this repeated code; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T58" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U58" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V58" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W58" s="66"/>
+    </x:row>
+    <x:row r="59" ht="52" customHeight="1">
+      <x:c r="A59" s="64" t="str">
+        <x:v>AM-KVN-045-1</x:v>
+      </x:c>
+      <x:c r="B59" s="65" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C59" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D59" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E59" s="71" t="str">
+        <x:v>50 Free Credits, TO 5, (All Games)</x:v>
+      </x:c>
+      <x:c r="F59" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="G59" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="H59" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I59" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J59" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K59" s="74"/>
+      <x:c r="L59" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M59" s="77"/>
+      <x:c r="N59" s="77"/>
+      <x:c r="O59" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P59" s="80"/>
+      <x:c r="Q59" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R59" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S59" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm shared or variable mechanics for this repeated code; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T59" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U59" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V59" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W59" s="66"/>
+    </x:row>
+    <x:row r="60" ht="52" customHeight="1">
+      <x:c r="A60" s="64" t="str">
+        <x:v>AM-KVN-046-1</x:v>
+      </x:c>
+      <x:c r="B60" s="65" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C60" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D60" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E60" s="71" t="str">
+        <x:v>60 Free Credits, TO 5, (All Games)</x:v>
+      </x:c>
+      <x:c r="F60" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="G60" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="H60" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I60" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J60" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K60" s="74"/>
+      <x:c r="L60" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M60" s="77"/>
+      <x:c r="N60" s="77"/>
+      <x:c r="O60" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P60" s="80"/>
+      <x:c r="Q60" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R60" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S60" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm shared or variable mechanics for this repeated code; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T60" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U60" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V60" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W60" s="66"/>
+    </x:row>
+    <x:row r="61" ht="52" customHeight="1">
+      <x:c r="A61" s="64" t="str">
+        <x:v>AM-KVN-047-1</x:v>
+      </x:c>
+      <x:c r="B61" s="65" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C61" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D61" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E61" s="71" t="str">
+        <x:v>160 Free Credits, TO 5, (All Games)</x:v>
+      </x:c>
+      <x:c r="F61" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="G61" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="H61" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I61" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J61" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K61" s="74"/>
+      <x:c r="L61" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M61" s="77"/>
+      <x:c r="N61" s="77"/>
+      <x:c r="O61" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P61" s="80"/>
+      <x:c r="Q61" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R61" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S61" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm shared or variable mechanics for this repeated code; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T61" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U61" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V61" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W61" s="66"/>
+    </x:row>
+    <x:row r="62" ht="52" customHeight="1">
+      <x:c r="A62" s="64" t="str">
+        <x:v>AM-KVN-048-1</x:v>
+      </x:c>
+      <x:c r="B62" s="65" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C62" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D62" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E62" s="71" t="str">
+        <x:v>200 Free Credits, TO 5, (All Games)</x:v>
+      </x:c>
+      <x:c r="F62" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="G62" s="71" t="str">
+        <x:v>VM_FC_VARIABLE_5X</x:v>
+      </x:c>
+      <x:c r="H62" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I62" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J62" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K62" s="74"/>
+      <x:c r="L62" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M62" s="77"/>
+      <x:c r="N62" s="77"/>
+      <x:c r="O62" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P62" s="80"/>
+      <x:c r="Q62" s="65" t="str">
+        <x:v>All Games</x:v>
+      </x:c>
+      <x:c r="R62" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S62" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm shared or variable mechanics for this repeated code; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T62" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U62" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V62" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W62" s="66"/>
+    </x:row>
+    <x:row r="63" ht="52" customHeight="1">
+      <x:c r="A63" s="64" t="str">
+        <x:v>AM-KVN-049-1</x:v>
+      </x:c>
+      <x:c r="B63" s="65" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C63" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D63" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E63" s="71" t="str">
+        <x:v>MYR 100 Deposit Match (5× TO)</x:v>
+      </x:c>
+      <x:c r="F63" s="71" t="str">
+        <x:v>VM_DEP300_GET100_5X</x:v>
+      </x:c>
+      <x:c r="G63" s="71" t="str">
+        <x:v>VM_DEP300_GET100_5X</x:v>
+      </x:c>
+      <x:c r="H63" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I63" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J63" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K63" s="74"/>
+      <x:c r="L63" s="77"/>
+      <x:c r="M63" s="77" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="N63" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O63" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P63" s="80"/>
+      <x:c r="Q63" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R63" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S63" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T63" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U63" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V63" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W63" s="66"/>
+    </x:row>
+    <x:row r="64" ht="52" customHeight="1">
+      <x:c r="A64" s="64" t="str">
+        <x:v>AM-KVN-050-1</x:v>
+      </x:c>
+      <x:c r="B64" s="65" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C64" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D64" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E64" s="71" t="str">
+        <x:v>MYR 200Deposit Match (5× TO)</x:v>
+      </x:c>
+      <x:c r="F64" s="71" t="str">
+        <x:v>VM_DEP600_GET200_5X</x:v>
+      </x:c>
+      <x:c r="G64" s="71" t="str">
+        <x:v>VM_DEP600_GET200_5X</x:v>
+      </x:c>
+      <x:c r="H64" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I64" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J64" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K64" s="74"/>
+      <x:c r="L64" s="77"/>
+      <x:c r="M64" s="77" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="N64" s="77" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="O64" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P64" s="80"/>
+      <x:c r="Q64" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R64" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S64" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T64" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U64" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V64" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W64" s="66"/>
+    </x:row>
+    <x:row r="65" ht="52" customHeight="1">
+      <x:c r="A65" s="64" t="str">
+        <x:v>AM-KVN-051-1</x:v>
+      </x:c>
+      <x:c r="B65" s="65" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C65" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D65" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E65" s="71" t="str">
+        <x:v>88 free spin, TO 1</x:v>
+      </x:c>
+      <x:c r="F65" s="71" t="str">
+        <x:v>CRM_ADHOC_NODEP_BDAY_FS_88_GOO</x:v>
+      </x:c>
+      <x:c r="G65" s="71" t="str">
+        <x:v>CRM_ADHOC_NODEP_BDAY_FS_88_GOO</x:v>
+      </x:c>
+      <x:c r="H65" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I65" s="65" t="str">
+        <x:v>Ad hoc (from code)</x:v>
+      </x:c>
+      <x:c r="J65" s="65" t="str">
+        <x:v>Free Spins</x:v>
+      </x:c>
+      <x:c r="K65" s="74"/>
+      <x:c r="L65" s="77" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="M65" s="77"/>
+      <x:c r="N65" s="77"/>
+      <x:c r="O65" s="65" t="str">
+        <x:v>1x</x:v>
+      </x:c>
+      <x:c r="P65" s="80"/>
+      <x:c r="Q65" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R65" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S65" s="71" t="str">
+        <x:v>Confirm site or brand; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T65" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U65" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V65" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W65" s="66"/>
+    </x:row>
+    <x:row r="66" ht="52" customHeight="1">
+      <x:c r="A66" s="64" t="str">
+        <x:v>AM-KVN-052-1</x:v>
+      </x:c>
+      <x:c r="B66" s="65" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C66" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D66" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E66" s="71"/>
+      <x:c r="F66" s="71" t="str">
+        <x:v>VM_DM_300_100_5X_14D</x:v>
+      </x:c>
+      <x:c r="G66" s="71" t="str">
+        <x:v>VM_DM_300_100_5X_14D</x:v>
+      </x:c>
+      <x:c r="H66" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I66" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J66" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K66" s="74"/>
+      <x:c r="L66" s="77"/>
+      <x:c r="M66" s="77" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="N66" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O66" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P66" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q66" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R66" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S66" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T66" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U66" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V66" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W66" s="66"/>
+    </x:row>
+    <x:row r="67" ht="52" customHeight="1">
+      <x:c r="A67" s="64" t="str">
+        <x:v>AM-KVN-053-1</x:v>
+      </x:c>
+      <x:c r="B67" s="65" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C67" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D67" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E67" s="71"/>
+      <x:c r="F67" s="71" t="str">
+        <x:v>VM_DM_1000_500_2X_14D</x:v>
+      </x:c>
+      <x:c r="G67" s="71" t="str">
+        <x:v>VM_DM_1000_500_2X_14D</x:v>
+      </x:c>
+      <x:c r="H67" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I67" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J67" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K67" s="74"/>
+      <x:c r="L67" s="77"/>
+      <x:c r="M67" s="77" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N67" s="77" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="O67" s="65" t="str">
+        <x:v>2x</x:v>
+      </x:c>
+      <x:c r="P67" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q67" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R67" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S67" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T67" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U67" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V67" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W67" s="66"/>
+    </x:row>
+    <x:row r="68" ht="52" customHeight="1">
+      <x:c r="A68" s="64" t="str">
+        <x:v>AM-KVN-054-1</x:v>
+      </x:c>
+      <x:c r="B68" s="65" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C68" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D68" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E68" s="71"/>
+      <x:c r="F68" s="71" t="str">
+        <x:v>VM_DM_800_400_2X_14D</x:v>
+      </x:c>
+      <x:c r="G68" s="71" t="str">
+        <x:v>VM_DM_800_400_2X_14D</x:v>
+      </x:c>
+      <x:c r="H68" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I68" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J68" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K68" s="74"/>
+      <x:c r="L68" s="77"/>
+      <x:c r="M68" s="77" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="N68" s="77" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="O68" s="65" t="str">
+        <x:v>2x</x:v>
+      </x:c>
+      <x:c r="P68" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q68" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R68" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S68" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T68" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U68" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V68" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W68" s="66"/>
+    </x:row>
+    <x:row r="69" ht="52" customHeight="1">
+      <x:c r="A69" s="64" t="str">
+        <x:v>AM-KVN-055-1</x:v>
+      </x:c>
+      <x:c r="B69" s="65" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C69" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D69" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E69" s="71"/>
+      <x:c r="F69" s="71" t="str">
+        <x:v>VM_DM_100_50_2X_14D</x:v>
+      </x:c>
+      <x:c r="G69" s="71" t="str">
+        <x:v>VM_DM_100_50_2X_14D</x:v>
+      </x:c>
+      <x:c r="H69" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I69" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J69" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K69" s="74"/>
+      <x:c r="L69" s="77"/>
+      <x:c r="M69" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N69" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O69" s="65" t="str">
+        <x:v>2x</x:v>
+      </x:c>
+      <x:c r="P69" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q69" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R69" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S69" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T69" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U69" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V69" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W69" s="66"/>
+    </x:row>
+    <x:row r="70" ht="52" customHeight="1">
+      <x:c r="A70" s="64" t="str">
+        <x:v>AM-KVN-056-1</x:v>
+      </x:c>
+      <x:c r="B70" s="65" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C70" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D70" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E70" s="71"/>
+      <x:c r="F70" s="71" t="str">
+        <x:v>VM_DM_1500_750_1X_14D</x:v>
+      </x:c>
+      <x:c r="G70" s="71" t="str">
+        <x:v>VM_DM_1500_750_1X_14D</x:v>
+      </x:c>
+      <x:c r="H70" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I70" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J70" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K70" s="74"/>
+      <x:c r="L70" s="77"/>
+      <x:c r="M70" s="77" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="N70" s="77" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="O70" s="65" t="str">
+        <x:v>1x</x:v>
+      </x:c>
+      <x:c r="P70" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q70" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R70" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S70" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T70" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U70" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V70" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W70" s="66"/>
+    </x:row>
+    <x:row r="71" ht="52" customHeight="1">
+      <x:c r="A71" s="64" t="str">
+        <x:v>AM-KVN-057-1</x:v>
+      </x:c>
+      <x:c r="B71" s="65" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C71" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D71" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E71" s="71"/>
+      <x:c r="F71" s="71" t="str">
+        <x:v>VM_DM_150_50_5X_14D</x:v>
+      </x:c>
+      <x:c r="G71" s="71" t="str">
+        <x:v>VM_DM_150_50_5X_14D</x:v>
+      </x:c>
+      <x:c r="H71" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I71" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J71" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K71" s="74"/>
+      <x:c r="L71" s="77"/>
+      <x:c r="M71" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="N71" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O71" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P71" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q71" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R71" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S71" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T71" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U71" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V71" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W71" s="66"/>
+    </x:row>
+    <x:row r="72" ht="52" customHeight="1">
+      <x:c r="A72" s="64" t="str">
+        <x:v>AM-KVN-058-1</x:v>
+      </x:c>
+      <x:c r="B72" s="65" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C72" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D72" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E72" s="71"/>
+      <x:c r="F72" s="71" t="str">
+        <x:v>VM_DM_2000_1000_2X_14D</x:v>
+      </x:c>
+      <x:c r="G72" s="71" t="str">
+        <x:v>VM_DM_2000_1000_2X_14D</x:v>
+      </x:c>
+      <x:c r="H72" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I72" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J72" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K72" s="74"/>
+      <x:c r="L72" s="77"/>
+      <x:c r="M72" s="77" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="N72" s="77" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="O72" s="65" t="str">
+        <x:v>2x</x:v>
+      </x:c>
+      <x:c r="P72" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q72" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R72" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S72" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T72" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U72" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V72" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W72" s="66"/>
+    </x:row>
+    <x:row r="73" ht="52" customHeight="1">
+      <x:c r="A73" s="64" t="str">
+        <x:v>AM-KVN-059-1</x:v>
+      </x:c>
+      <x:c r="B73" s="65" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C73" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D73" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E73" s="71"/>
+      <x:c r="F73" s="71" t="str">
+        <x:v>VM_DM_700_350_2X_14D</x:v>
+      </x:c>
+      <x:c r="G73" s="71" t="str">
+        <x:v>VM_DM_700_350_2X_14D</x:v>
+      </x:c>
+      <x:c r="H73" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I73" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J73" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K73" s="74"/>
+      <x:c r="L73" s="77"/>
+      <x:c r="M73" s="77" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="N73" s="77" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="O73" s="65" t="str">
+        <x:v>2x</x:v>
+      </x:c>
+      <x:c r="P73" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q73" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R73" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S73" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T73" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U73" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V73" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W73" s="66"/>
+    </x:row>
+    <x:row r="74" ht="52" customHeight="1">
+      <x:c r="A74" s="64" t="str">
+        <x:v>AM-KVN-060-1</x:v>
+      </x:c>
+      <x:c r="B74" s="65" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C74" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D74" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E74" s="71"/>
+      <x:c r="F74" s="71" t="str">
+        <x:v>VM_DM_1000_300_5X_14D</x:v>
+      </x:c>
+      <x:c r="G74" s="71" t="str">
+        <x:v>VM_DM_1000_300_5X_14D</x:v>
+      </x:c>
+      <x:c r="H74" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I74" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J74" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K74" s="74"/>
+      <x:c r="L74" s="77"/>
+      <x:c r="M74" s="77" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="N74" s="77" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="O74" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P74" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q74" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R74" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S74" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T74" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U74" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V74" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W74" s="66"/>
+    </x:row>
+    <x:row r="75" ht="52" customHeight="1">
+      <x:c r="A75" s="64" t="str">
+        <x:v>AM-KVN-061-1</x:v>
+      </x:c>
+      <x:c r="B75" s="65" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C75" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D75" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E75" s="71"/>
+      <x:c r="F75" s="71" t="str">
+        <x:v>VM_DM_200_100_2X_7D</x:v>
+      </x:c>
+      <x:c r="G75" s="71" t="str">
+        <x:v>VM_DM_200_100_2X_7D</x:v>
+      </x:c>
+      <x:c r="H75" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I75" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J75" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K75" s="74"/>
+      <x:c r="L75" s="77"/>
+      <x:c r="M75" s="77" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="N75" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O75" s="65" t="str">
+        <x:v>2x</x:v>
+      </x:c>
+      <x:c r="P75" s="80" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q75" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R75" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S75" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T75" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U75" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V75" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W75" s="66"/>
+    </x:row>
+    <x:row r="76" ht="52" customHeight="1">
+      <x:c r="A76" s="64" t="str">
+        <x:v>AM-KVN-062-1</x:v>
+      </x:c>
+      <x:c r="B76" s="65" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C76" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D76" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E76" s="71"/>
+      <x:c r="F76" s="71" t="str">
+        <x:v>VM_FC_50_5X_14D</x:v>
+      </x:c>
+      <x:c r="G76" s="71" t="str">
+        <x:v>VM_FC_50_5X_14D</x:v>
+      </x:c>
+      <x:c r="H76" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I76" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J76" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K76" s="74"/>
+      <x:c r="L76" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M76" s="77"/>
+      <x:c r="N76" s="77"/>
+      <x:c r="O76" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P76" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q76" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R76" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S76" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T76" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U76" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V76" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W76" s="66"/>
+    </x:row>
+    <x:row r="77" ht="52" customHeight="1">
+      <x:c r="A77" s="64" t="str">
+        <x:v>AM-KVN-063-1</x:v>
+      </x:c>
+      <x:c r="B77" s="65" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C77" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D77" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E77" s="71"/>
+      <x:c r="F77" s="71" t="str">
+        <x:v>VM_DM_100_30_5X_14D</x:v>
+      </x:c>
+      <x:c r="G77" s="71" t="str">
+        <x:v>VM_DM_100_30_5X_14D</x:v>
+      </x:c>
+      <x:c r="H77" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I77" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J77" s="65" t="str">
+        <x:v>Deposit Bonus</x:v>
+      </x:c>
+      <x:c r="K77" s="74"/>
+      <x:c r="L77" s="77"/>
+      <x:c r="M77" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N77" s="77" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O77" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P77" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q77" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R77" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S77" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T77" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U77" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V77" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W77" s="66"/>
+    </x:row>
+    <x:row r="78" ht="52" customHeight="1">
+      <x:c r="A78" s="64" t="str">
+        <x:v>AM-KVN-064-1</x:v>
+      </x:c>
+      <x:c r="B78" s="65" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C78" s="65" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D78" s="65" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E78" s="71"/>
+      <x:c r="F78" s="71" t="str">
+        <x:v>VM_FC_388_5X_14D</x:v>
+      </x:c>
+      <x:c r="G78" s="71" t="str">
+        <x:v>VM_FC_388_5X_14D</x:v>
+      </x:c>
+      <x:c r="H78" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I78" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J78" s="65" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K78" s="74"/>
+      <x:c r="L78" s="77" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="M78" s="77"/>
+      <x:c r="N78" s="77"/>
+      <x:c r="O78" s="65" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P78" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q78" s="65" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R78" s="65" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S78" s="71" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T78" s="71" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U78" s="83" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V78" s="65" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W78" s="66"/>
+    </x:row>
+    <x:row r="79" ht="52" customHeight="1">
+      <x:c r="A79" s="67" t="str">
+        <x:v>AM-KVN-065-1</x:v>
+      </x:c>
+      <x:c r="B79" s="68" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C79" s="68" t="str">
+        <x:v>AM Team</x:v>
+      </x:c>
+      <x:c r="D79" s="68" t="str">
+        <x:v>Kevin</x:v>
+      </x:c>
+      <x:c r="E79" s="72"/>
+      <x:c r="F79" s="72" t="str">
+        <x:v>VM_FC_188_5X_14D</x:v>
+      </x:c>
+      <x:c r="G79" s="72" t="str">
+        <x:v>VM_FC_188_5X_14D</x:v>
+      </x:c>
+      <x:c r="H79" s="68" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="I79" s="68" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="J79" s="68" t="str">
+        <x:v>Free Credit</x:v>
+      </x:c>
+      <x:c r="K79" s="75"/>
+      <x:c r="L79" s="78" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="M79" s="78"/>
+      <x:c r="N79" s="78"/>
+      <x:c r="O79" s="68" t="str">
+        <x:v>5x</x:v>
+      </x:c>
+      <x:c r="P79" s="81" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q79" s="68" t="str">
+        <x:v>Not provided</x:v>
+      </x:c>
+      <x:c r="R79" s="68" t="str">
+        <x:v>Available</x:v>
+      </x:c>
+      <x:c r="S79" s="72" t="str">
+        <x:v>Bonus mechanic is missing; Confirm site or brand; Confirm monthly or ad hoc; Confirm active period, objective and target segment.</x:v>
+      </x:c>
+      <x:c r="T79" s="72" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1VIdshikD-J3Bq9SoKMEQy80f1fCM39p69RSTOlaJDgE</x:v>
+      </x:c>
+      <x:c r="U79" s="84" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="V79" s="68" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="W79" s="69"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:W1"/>
+    <x:mergeCell ref="A2:W2"/>
+    <x:mergeCell ref="A3:W3"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="R7:R79">
+    <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Missing"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="V7:V79">
+    <x:cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Yes"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I7:I79">
+      <x:formula1>"Monthly,Ad hoc,Ad hoc (from code),Not provided"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1263130ca084ac4"/>
+  </x:tableParts>
+</x:worksheet>
 </file>